--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\XYRogueLike_ET\XYRogueLike_ET\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A263A66-5832-467D-B8A4-4C249B5E388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68429E03-AC8B-4711-B7CC-BADD0CDD447C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="31">
   <si>
     <t>Id</t>
   </si>
@@ -82,12 +82,6 @@
   </si>
   <si>
     <t>Map</t>
-  </si>
-  <si>
-    <t>Map1</t>
-  </si>
-  <si>
-    <t>Map2</t>
   </si>
   <si>
     <t>RouterManager</t>
@@ -122,6 +116,10 @@
   <si>
     <t>#公共服，用来存放用户信息等公共配置将登录时用到的Realm服务器迁移到公共服</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HomeScene</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -606,7 +604,7 @@
     </row>
     <row r="6" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -717,7 +715,7 @@
         <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -735,7 +733,7 @@
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H12" s="5"/>
     </row>
@@ -830,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H6" s="5">
         <v>30300</v>
@@ -850,10 +848,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H7" s="5">
         <v>30301</v>
@@ -870,10 +868,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="H8" s="5">
         <v>30302</v>
@@ -890,10 +888,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H9" s="5">
         <v>30303</v>
@@ -910,10 +908,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H10" s="5">
         <v>30304</v>
@@ -940,7 +938,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1014,10 +1012,10 @@
         <v>1000</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.3">
@@ -1031,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" s="5">
         <v>30002</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68429E03-AC8B-4711-B7CC-BADD0CDD447C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB097DC-8303-446D-8844-78BD7B4876F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4464" yWindow="5532" windowWidth="23040" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -119,6 +119,10 @@
   </si>
   <si>
     <t>HomeScene</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -733,7 +737,7 @@
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" s="5"/>
     </row>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB097DC-8303-446D-8844-78BD7B4876F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F9A9E4-DE4A-4088-BA51-7158E0282976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4464" yWindow="5532" windowWidth="23040" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4428" yWindow="4008" windowWidth="23040" windowHeight="12660" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F9A9E4-DE4A-4088-BA51-7158E0282976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E3D0A8-3CA3-4D6E-8F03-91BDF1A9BB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4428" yWindow="4008" windowWidth="23040" windowHeight="12660" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -123,6 +123,10 @@
   </si>
   <si>
     <t>Map2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:H12"/>
+  <dimension ref="B3:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -740,6 +744,23 @@
         <v>31</v>
       </c>
       <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="5">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
